--- a/rti_database.xlsx
+++ b/rti_database.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Personal_Projects\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Personal_Projects\Git_Repo\online_rti_automation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0746B84-EBC8-4EDC-9499-8351E616C21C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D307B42B-8D08-4881-9C72-45F71509CC25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="RTI Departments" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'RTI Departments'!$D$1:$D$2905</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'RTI Departments'!$A$1:$D$2905</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
@@ -17816,16 +17816,16 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
